--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/86.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/86.xlsx
@@ -426,13 +426,13 @@
         <v>-5.960448155132555</v>
       </c>
       <c r="E2">
-        <v>-2.852025357933956</v>
+        <v>-6.7163185369508</v>
       </c>
       <c r="F2">
-        <v>-1.510116407653215</v>
+        <v>-1.981374623105854</v>
       </c>
       <c r="G2">
-        <v>-10.36195858338804</v>
+        <v>-10.93652342076648</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.491326246497287</v>
       </c>
       <c r="E3">
-        <v>-3.710602122270461</v>
+        <v>-7.336135488645562</v>
       </c>
       <c r="F3">
-        <v>-1.870929225657998</v>
+        <v>-2.054613898656969</v>
       </c>
       <c r="G3">
-        <v>-10.65126955062456</v>
+        <v>-10.45640487971616</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.818224277171082</v>
       </c>
       <c r="E4">
-        <v>-6.227369274101386</v>
+        <v>-8.716700311920492</v>
       </c>
       <c r="F4">
-        <v>-2.037599232203467</v>
+        <v>-2.224212183971334</v>
       </c>
       <c r="G4">
-        <v>-9.403246176128603</v>
+        <v>-9.757992845796782</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.002933327797713</v>
       </c>
       <c r="E5">
-        <v>-6.650652112693936</v>
+        <v>-9.228915864611597</v>
       </c>
       <c r="F5">
-        <v>-1.54189423795941</v>
+        <v>-2.099319230651253</v>
       </c>
       <c r="G5">
-        <v>-9.334424337962266</v>
+        <v>-9.728349146336985</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.046042487870822</v>
       </c>
       <c r="E6">
-        <v>-6.838580771931102</v>
+        <v>-9.72489236102262</v>
       </c>
       <c r="F6">
-        <v>-1.444401193221727</v>
+        <v>-2.220126675940727</v>
       </c>
       <c r="G6">
-        <v>-8.594002812827288</v>
+        <v>-8.607933745965468</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.981268440173072</v>
       </c>
       <c r="E7">
-        <v>-8.449191970488286</v>
+        <v>-10.90242744868331</v>
       </c>
       <c r="F7">
-        <v>-1.408681990813013</v>
+        <v>-2.07656977666817</v>
       </c>
       <c r="G7">
-        <v>-8.653792780080668</v>
+        <v>-8.374158537671114</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.8305848805871968</v>
       </c>
       <c r="E8">
-        <v>-9.258245842987536</v>
+        <v>-12.00316135252527</v>
       </c>
       <c r="F8">
-        <v>-1.639453552089316</v>
+        <v>-2.169581353756707</v>
       </c>
       <c r="G8">
-        <v>-7.726093407819064</v>
+        <v>-7.433492902397747</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>0.3745047344277651</v>
       </c>
       <c r="E9">
-        <v>-10.09203208892614</v>
+        <v>-12.96085865834013</v>
       </c>
       <c r="F9">
-        <v>-1.306222883495547</v>
+        <v>-2.263000487607421</v>
       </c>
       <c r="G9">
-        <v>-7.130294079308806</v>
+        <v>-6.592707828318896</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>1.606690363357328</v>
       </c>
       <c r="E10">
-        <v>-12.33369882902307</v>
+        <v>-13.88232334855719</v>
       </c>
       <c r="F10">
-        <v>-0.9734320779926656</v>
+        <v>-2.402109882294348</v>
       </c>
       <c r="G10">
-        <v>-6.093136629320187</v>
+        <v>-5.672328983890774</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>2.829894087743813</v>
       </c>
       <c r="E11">
-        <v>-11.03531775144385</v>
+        <v>-15.17110220155341</v>
       </c>
       <c r="F11">
-        <v>-1.113332563549266</v>
+        <v>-2.232714546993668</v>
       </c>
       <c r="G11">
-        <v>-4.899227463336534</v>
+        <v>-5.14868933050659</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>4.000321904059907</v>
       </c>
       <c r="E12">
-        <v>-12.52685222810687</v>
+        <v>-15.69477646428972</v>
       </c>
       <c r="F12">
-        <v>-1.244077104202723</v>
+        <v>-2.613143105096744</v>
       </c>
       <c r="G12">
-        <v>-4.358414332032008</v>
+        <v>-4.403888281320019</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>5.067718700578352</v>
       </c>
       <c r="E13">
-        <v>-13.18171397696054</v>
+        <v>-17.01578839037793</v>
       </c>
       <c r="F13">
-        <v>-1.330405413085473</v>
+        <v>-2.536491784213498</v>
       </c>
       <c r="G13">
-        <v>-4.383049317993753</v>
+        <v>-3.590683113101688</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>5.984932648390489</v>
       </c>
       <c r="E14">
-        <v>-15.64161951254323</v>
+        <v>-18.46638050980079</v>
       </c>
       <c r="F14">
-        <v>-1.272098288337222</v>
+        <v>-2.439900831577464</v>
       </c>
       <c r="G14">
-        <v>-3.639639795674245</v>
+        <v>-2.597900488928222</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>6.718067028389396</v>
       </c>
       <c r="E15">
-        <v>-15.75840781499741</v>
+        <v>-19.6665007606459</v>
       </c>
       <c r="F15">
-        <v>-0.7942305293776457</v>
+        <v>-2.510105797332125</v>
       </c>
       <c r="G15">
-        <v>-3.00028933126733</v>
+        <v>-2.030695340552131</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>7.25472093369619</v>
       </c>
       <c r="E16">
-        <v>-16.74698424701237</v>
+        <v>-21.13900522301856</v>
       </c>
       <c r="F16">
-        <v>-0.5455786577119154</v>
+        <v>-2.64396831288972</v>
       </c>
       <c r="G16">
-        <v>-1.419953415374636</v>
+        <v>-1.594761040961808</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>7.606431188901896</v>
       </c>
       <c r="E17">
-        <v>-17.46534029060002</v>
+        <v>-21.43427778215725</v>
       </c>
       <c r="F17">
-        <v>-0.6266551172609169</v>
+        <v>-2.184891240095247</v>
       </c>
       <c r="G17">
-        <v>-1.523884546802265</v>
+        <v>-1.059409587341891</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>7.802622854813852</v>
       </c>
       <c r="E18">
-        <v>-18.30337527172392</v>
+        <v>-22.31160214241402</v>
       </c>
       <c r="F18">
-        <v>-0.6805611259980948</v>
+        <v>-2.158578149545321</v>
       </c>
       <c r="G18">
-        <v>-0.9181421975167512</v>
+        <v>-0.7221823192523791</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>7.877379631496341</v>
       </c>
       <c r="E19">
-        <v>-19.83550323587582</v>
+        <v>-23.62462328991327</v>
       </c>
       <c r="F19">
-        <v>-0.5848871760769603</v>
+        <v>-1.931581458523575</v>
       </c>
       <c r="G19">
-        <v>-1.074066307476401</v>
+        <v>-0.6579371163542633</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>7.860906206171667</v>
       </c>
       <c r="E20">
-        <v>-21.4352911657205</v>
+        <v>-24.26229074388214</v>
       </c>
       <c r="F20">
-        <v>-0.2381284394280732</v>
+        <v>-1.838668457155971</v>
       </c>
       <c r="G20">
-        <v>-0.02563827308794554</v>
+        <v>0.112256034725476</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>7.782459358549516</v>
       </c>
       <c r="E21">
-        <v>-21.27778893264903</v>
+        <v>-25.53479316169636</v>
       </c>
       <c r="F21">
-        <v>0.6308422199870529</v>
+        <v>-1.789958797136555</v>
       </c>
       <c r="G21">
-        <v>-0.3619178408908834</v>
+        <v>0.03820226439854763</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>7.661545803055759</v>
       </c>
       <c r="E22">
-        <v>-21.70098455380376</v>
+        <v>-25.90832883504012</v>
       </c>
       <c r="F22">
-        <v>0.5227717518830238</v>
+        <v>-1.497936921729854</v>
       </c>
       <c r="G22">
-        <v>0.1522317559046026</v>
+        <v>-0.3792192452961912</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>7.507766011445066</v>
       </c>
       <c r="E23">
-        <v>-21.2814645246715</v>
+        <v>-26.03841987336772</v>
       </c>
       <c r="F23">
-        <v>-0.02090896886157007</v>
+        <v>-1.378105293240877</v>
       </c>
       <c r="G23">
-        <v>-0.3566336938384702</v>
+        <v>-0.3869835997101621</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>7.333129538558089</v>
       </c>
       <c r="E24">
-        <v>-23.52887100281935</v>
+        <v>-26.91084759747253</v>
       </c>
       <c r="F24">
-        <v>0.6668886275198734</v>
+        <v>-0.9713354800961801</v>
       </c>
       <c r="G24">
-        <v>-0.5363547407461177</v>
+        <v>-1.064884318749456</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>7.147492918268962</v>
       </c>
       <c r="E25">
-        <v>-22.79446279746124</v>
+        <v>-26.84101550225686</v>
       </c>
       <c r="F25">
-        <v>0.408296347020549</v>
+        <v>-1.265754650766583</v>
       </c>
       <c r="G25">
-        <v>-0.9850895210666691</v>
+        <v>-0.8783805573940958</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>6.958326515155706</v>
       </c>
       <c r="E26">
-        <v>-23.42219576994113</v>
+        <v>-26.91203541591143</v>
       </c>
       <c r="F26">
-        <v>0.4948002697926929</v>
+        <v>-1.216553768877306</v>
       </c>
       <c r="G26">
-        <v>-0.6830368148532264</v>
+        <v>-0.8504690869705037</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>6.776377494623663</v>
       </c>
       <c r="E27">
-        <v>-23.55446309100294</v>
+        <v>-27.16296829094625</v>
       </c>
       <c r="F27">
-        <v>0.3953804424760991</v>
+        <v>-1.060730405104094</v>
       </c>
       <c r="G27">
-        <v>-0.5392004523504311</v>
+        <v>-1.480543575845193</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>6.617294211898284</v>
       </c>
       <c r="E28">
-        <v>-21.90057127722972</v>
+        <v>-27.17483401570128</v>
       </c>
       <c r="F28">
-        <v>0.1254395285584214</v>
+        <v>-1.067359001061296</v>
       </c>
       <c r="G28">
-        <v>-0.8854687289589684</v>
+        <v>-1.720395292175362</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>6.493040929348551</v>
       </c>
       <c r="E29">
-        <v>-22.26709632985716</v>
+        <v>-26.95698562208005</v>
       </c>
       <c r="F29">
-        <v>0.5308822971238338</v>
+        <v>-1.040990409895382</v>
       </c>
       <c r="G29">
-        <v>-0.4316691041316571</v>
+        <v>-1.626293614133274</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>6.412127888261501</v>
       </c>
       <c r="E30">
-        <v>-22.75249044381252</v>
+        <v>-26.23084230725835</v>
       </c>
       <c r="F30">
-        <v>0.415885849164998</v>
+        <v>-1.136028173651167</v>
       </c>
       <c r="G30">
-        <v>-1.351632840169792</v>
+        <v>-1.956336113108043</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>6.394576597178643</v>
       </c>
       <c r="E31">
-        <v>-21.94274713823335</v>
+        <v>-26.98348726354378</v>
       </c>
       <c r="F31">
-        <v>0.1475859310722662</v>
+        <v>-0.9774471747940348</v>
       </c>
       <c r="G31">
-        <v>-1.244161539076614</v>
+        <v>-1.80798055171803</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>6.451333289722182</v>
       </c>
       <c r="E32">
-        <v>-22.26810971342042</v>
+        <v>-26.03961184501794</v>
       </c>
       <c r="F32">
-        <v>0.7910932075282285</v>
+        <v>-1.220843883656405</v>
       </c>
       <c r="G32">
-        <v>-1.938898949983997</v>
+        <v>-2.391147792524187</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>6.581404125275746</v>
       </c>
       <c r="E33">
-        <v>-21.6019138508613</v>
+        <v>-25.50618168887962</v>
       </c>
       <c r="F33">
-        <v>0.5090539876926641</v>
+        <v>-1.278417074885776</v>
       </c>
       <c r="G33">
-        <v>-1.817188647890887</v>
+        <v>-1.872121324832501</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>6.779845386738661</v>
       </c>
       <c r="E34">
-        <v>-20.54902078827004</v>
+        <v>-25.98067777631863</v>
       </c>
       <c r="F34">
-        <v>-0.2171715725046486</v>
+        <v>-0.9607638553016528</v>
       </c>
       <c r="G34">
-        <v>-1.987858243301144</v>
+        <v>-1.716348638059136</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>7.029465265320282</v>
       </c>
       <c r="E35">
-        <v>-20.54067698671846</v>
+        <v>-24.57497771810583</v>
       </c>
       <c r="F35">
-        <v>0.0732954572869981</v>
+        <v>-0.9074062257851282</v>
       </c>
       <c r="G35">
-        <v>-1.714006800160907</v>
+        <v>-2.045821994713041</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>7.299247828414893</v>
       </c>
       <c r="E36">
-        <v>-19.68602085387259</v>
+        <v>-24.05693936313732</v>
       </c>
       <c r="F36">
-        <v>0.5234501847859167</v>
+        <v>-0.9792256796078453</v>
       </c>
       <c r="G36">
-        <v>-1.546506648684261</v>
+        <v>-2.26344061010529</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>7.552404330666827</v>
       </c>
       <c r="E37">
-        <v>-18.89454337170002</v>
+        <v>-23.67175808523875</v>
       </c>
       <c r="F37">
-        <v>0.7650443661797952</v>
+        <v>-1.025731882335815</v>
       </c>
       <c r="G37">
-        <v>-1.198572717026594</v>
+        <v>-2.202832174422594</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>7.757885414610151</v>
       </c>
       <c r="E38">
-        <v>-18.77525483602829</v>
+        <v>-23.23486101992341</v>
       </c>
       <c r="F38">
-        <v>0.4536519474260303</v>
+        <v>-1.000011074478891</v>
       </c>
       <c r="G38">
-        <v>-1.366869145603529</v>
+        <v>-1.956625905757656</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>7.887772371537206</v>
       </c>
       <c r="E39">
-        <v>-18.27422803464628</v>
+        <v>-22.8718869629787</v>
       </c>
       <c r="F39">
-        <v>0.1237405470152796</v>
+        <v>-0.9499569741647304</v>
       </c>
       <c r="G39">
-        <v>-2.123026933761444</v>
+        <v>-1.826151334072179</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>7.921345998290469</v>
       </c>
       <c r="E40">
-        <v>-16.75886658461271</v>
+        <v>-21.66447782625852</v>
       </c>
       <c r="F40">
-        <v>0.740928934349496</v>
+        <v>-0.7305754646769206</v>
       </c>
       <c r="G40">
-        <v>-1.950835274254567</v>
+        <v>-1.872570372902173</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>7.857304912068913</v>
       </c>
       <c r="E41">
-        <v>-15.85379461949475</v>
+        <v>-20.37063205544601</v>
       </c>
       <c r="F41">
-        <v>0.632193287221019</v>
+        <v>-0.7874901038210662</v>
       </c>
       <c r="G41">
-        <v>-1.672819693491504</v>
+        <v>-1.837273106030321</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>7.701159334418906</v>
       </c>
       <c r="E42">
-        <v>-16.05651286425963</v>
+        <v>-20.25457471818499</v>
       </c>
       <c r="F42">
-        <v>0.5514291221828728</v>
+        <v>-0.7461545704213708</v>
       </c>
       <c r="G42">
-        <v>-1.68591779910512</v>
+        <v>-2.062533370840758</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>7.464272446386588</v>
       </c>
       <c r="E43">
-        <v>-16.01134669110212</v>
+        <v>-20.08335442810762</v>
       </c>
       <c r="F43">
-        <v>0.916841036007999</v>
+        <v>-0.7839132133757779</v>
       </c>
       <c r="G43">
-        <v>-2.382046736879566</v>
+        <v>-2.077960260629646</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>7.166694331448242</v>
       </c>
       <c r="E44">
-        <v>-14.74045156607061</v>
+        <v>-18.03055081979593</v>
       </c>
       <c r="F44">
-        <v>0.6193345400273622</v>
+        <v>-0.819981986828474</v>
       </c>
       <c r="G44">
-        <v>-1.741986149943868</v>
+        <v>-2.456667038782766</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>6.829823770077401</v>
       </c>
       <c r="E45">
-        <v>-14.19599878707619</v>
+        <v>-18.1979709215111</v>
       </c>
       <c r="F45">
-        <v>0.427024905630443</v>
+        <v>-0.4340605244774347</v>
       </c>
       <c r="G45">
-        <v>-2.437720865285057</v>
+        <v>-2.634698933939963</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>6.470518894940736</v>
       </c>
       <c r="E46">
-        <v>-13.84165095005314</v>
+        <v>-17.32506142489261</v>
       </c>
       <c r="F46">
-        <v>0.5960226245777785</v>
+        <v>-0.7805061382480636</v>
       </c>
       <c r="G46">
-        <v>-2.405347632355252</v>
+        <v>-2.772188576341762</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>6.101790180179129</v>
       </c>
       <c r="E47">
-        <v>-13.1292506115053</v>
+        <v>-15.86273648347711</v>
       </c>
       <c r="F47">
-        <v>0.5217188969140657</v>
+        <v>-0.7749105164421529</v>
       </c>
       <c r="G47">
-        <v>-2.746141177556225</v>
+        <v>-3.668572067232962</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>5.736688475000628</v>
       </c>
       <c r="E48">
-        <v>-11.88102371388471</v>
+        <v>-14.8921185372307</v>
       </c>
       <c r="F48">
-        <v>0.5923090535110284</v>
+        <v>-0.4936615591088591</v>
       </c>
       <c r="G48">
-        <v>-2.881578774709409</v>
+        <v>-3.498153103303451</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>5.37960159868361</v>
       </c>
       <c r="E49">
-        <v>-11.57335797215273</v>
+        <v>-14.92020255220919</v>
       </c>
       <c r="F49">
-        <v>0.782625635936812</v>
+        <v>-0.8421051950550403</v>
       </c>
       <c r="G49">
-        <v>-2.752644542332688</v>
+        <v>-3.746583726360018</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>5.027246909137522</v>
       </c>
       <c r="E50">
-        <v>-9.667852156687426</v>
+        <v>-14.19108138486759</v>
       </c>
       <c r="F50">
-        <v>0.5750367647952559</v>
+        <v>-0.5901589062283763</v>
       </c>
       <c r="G50">
-        <v>-3.586641680474645</v>
+        <v>-4.081054048161315</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>4.682546384391324</v>
       </c>
       <c r="E51">
-        <v>-10.05979901583414</v>
+        <v>-13.2655631603975</v>
       </c>
       <c r="F51">
-        <v>0.2653309020735907</v>
+        <v>-0.6450357615616352</v>
       </c>
       <c r="G51">
-        <v>-3.302550897048062</v>
+        <v>-4.287488233725234</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.346811619220103</v>
       </c>
       <c r="E52">
-        <v>-9.327720762029267</v>
+        <v>-12.27813716791951</v>
       </c>
       <c r="F52">
-        <v>0.6178476205393371</v>
+        <v>-0.7522861459368928</v>
       </c>
       <c r="G52">
-        <v>-3.99408753508674</v>
+        <v>-4.030040098850961</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>4.019895139922204</v>
       </c>
       <c r="E53">
-        <v>-9.821558354608005</v>
+        <v>-12.5521162125958</v>
       </c>
       <c r="F53">
-        <v>0.5630908784794841</v>
+        <v>-0.4995338556273048</v>
       </c>
       <c r="G53">
-        <v>-3.910700352846582</v>
+        <v>-4.243959289157601</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>3.703607496202331</v>
       </c>
       <c r="E54">
-        <v>-8.080540473662531</v>
+        <v>-10.32859900598837</v>
       </c>
       <c r="F54">
-        <v>0.6348076147442542</v>
+        <v>-0.7316448869939347</v>
       </c>
       <c r="G54">
-        <v>-3.552242509742136</v>
+        <v>-4.573309940815725</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>3.401983394412803</v>
       </c>
       <c r="E55">
-        <v>-7.025658022846679</v>
+        <v>-11.19839774732456</v>
       </c>
       <c r="F55">
-        <v>0.5883792785521474</v>
+        <v>-0.5328657031811513</v>
       </c>
       <c r="G55">
-        <v>-3.870374791892246</v>
+        <v>-5.302556173728443</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>3.118686894939353</v>
       </c>
       <c r="E56">
-        <v>-6.42649499107029</v>
+        <v>-9.395567622231667</v>
       </c>
       <c r="F56">
-        <v>0.1955268661418847</v>
+        <v>-0.6563993055932388</v>
       </c>
       <c r="G56">
-        <v>-4.432306236194287</v>
+        <v>-5.343103647973024</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>2.856055467755205</v>
       </c>
       <c r="E57">
-        <v>-7.105250164675693</v>
+        <v>-9.035056419602574</v>
       </c>
       <c r="F57">
-        <v>0.5551998506004161</v>
+        <v>-0.6922170837228866</v>
       </c>
       <c r="G57">
-        <v>-4.699643871579696</v>
+        <v>-5.237532968942175</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>2.619582415492252</v>
       </c>
       <c r="E58">
-        <v>-5.639664952370198</v>
+        <v>-8.868001800483997</v>
       </c>
       <c r="F58">
-        <v>0.6902411329721942</v>
+        <v>-0.52832624981381</v>
       </c>
       <c r="G58">
-        <v>-5.594312103274535</v>
+        <v>-6.011041765652629</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>2.411031399697549</v>
       </c>
       <c r="E59">
-        <v>-4.725293947095945</v>
+        <v>-8.323362126979955</v>
       </c>
       <c r="F59">
-        <v>0.4804206400474964</v>
+        <v>-0.4818117634118122</v>
       </c>
       <c r="G59">
-        <v>-5.384794628348511</v>
+        <v>-5.799743762915466</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>2.228824446523904</v>
       </c>
       <c r="E60">
-        <v>-4.521695221530201</v>
+        <v>-7.685582536305311</v>
       </c>
       <c r="F60">
-        <v>0.4587778849145536</v>
+        <v>-0.7116895162604946</v>
       </c>
       <c r="G60">
-        <v>-4.977226068740634</v>
+        <v>-6.201740993565908</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>2.071639285753468</v>
       </c>
       <c r="E61">
-        <v>-5.334947990678852</v>
+        <v>-7.283111439661476</v>
       </c>
       <c r="F61">
-        <v>0.7054126819544673</v>
+        <v>-0.86617340994338</v>
       </c>
       <c r="G61">
-        <v>-5.376079962903376</v>
+        <v>-6.259373180414734</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.933225083583442</v>
       </c>
       <c r="E62">
-        <v>-4.589159986290716</v>
+        <v>-6.869700784388042</v>
       </c>
       <c r="F62">
-        <v>0.8771059084305124</v>
+        <v>-0.9106617096781302</v>
       </c>
       <c r="G62">
-        <v>-5.010338142389724</v>
+        <v>-6.469125622353957</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>1.804443374914419</v>
       </c>
       <c r="E63">
-        <v>-3.10323234491621</v>
+        <v>-5.534435037033017</v>
       </c>
       <c r="F63">
-        <v>0.5701725914060172</v>
+        <v>-0.5509133437859441</v>
       </c>
       <c r="G63">
-        <v>-5.372490189090595</v>
+        <v>-6.862452570217312</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>1.675087792136089</v>
       </c>
       <c r="E64">
-        <v>-3.298910896485507</v>
+        <v>-6.152503486760025</v>
       </c>
       <c r="F64">
-        <v>0.2317762236883911</v>
+        <v>-0.8909896405964476</v>
       </c>
       <c r="G64">
-        <v>-5.4991374092055</v>
+        <v>-7.217714861942234</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>1.533933892389653</v>
       </c>
       <c r="E65">
-        <v>-3.168753406776705</v>
+        <v>-5.206916945168363</v>
       </c>
       <c r="F65">
-        <v>0.2475218312808041</v>
+        <v>-0.7382883935643867</v>
       </c>
       <c r="G65">
-        <v>-6.776112635844604</v>
+        <v>-6.764299016569816</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>1.37008138510849</v>
       </c>
       <c r="E66">
-        <v>-3.436091466544593</v>
+        <v>-5.638485440353946</v>
       </c>
       <c r="F66">
-        <v>0.2012119516272978</v>
+        <v>-0.8380958968254908</v>
       </c>
       <c r="G66">
-        <v>-6.129478194028483</v>
+        <v>-7.083559140383286</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>1.175956159763392</v>
       </c>
       <c r="E67">
-        <v>-2.260599758855721</v>
+        <v>-5.747918405551854</v>
       </c>
       <c r="F67">
-        <v>0.5973032805825066</v>
+        <v>-1.034964037040016</v>
       </c>
       <c r="G67">
-        <v>-5.667914214787201</v>
+        <v>-6.621486065946737</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.9491308831582619</v>
       </c>
       <c r="E68">
-        <v>-3.271512161375613</v>
+        <v>-4.747596691910275</v>
       </c>
       <c r="F68">
-        <v>0.5271794948333201</v>
+        <v>-0.9104016023136512</v>
       </c>
       <c r="G68">
-        <v>-5.534069171834596</v>
+        <v>-7.027221882851653</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.6902581430007587</v>
       </c>
       <c r="E69">
-        <v>-2.764326147598876</v>
+        <v>-4.754121386901581</v>
       </c>
       <c r="F69">
-        <v>-0.109235299919873</v>
+        <v>-1.026905678945582</v>
       </c>
       <c r="G69">
-        <v>-6.480769543230323</v>
+        <v>-6.477495669513067</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.4039721150166977</v>
       </c>
       <c r="E70">
-        <v>-2.785200187717464</v>
+        <v>-5.16737422014467</v>
       </c>
       <c r="F70">
-        <v>-0.2029576162400118</v>
+        <v>-0.7216042457046019</v>
       </c>
       <c r="G70">
-        <v>-6.230161559184767</v>
+        <v>-6.530449402054617</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.09970035728589052</v>
       </c>
       <c r="E71">
-        <v>-2.205025638118191</v>
+        <v>-5.200574991475349</v>
       </c>
       <c r="F71">
-        <v>0.479331336912815</v>
+        <v>-1.091297162267396</v>
       </c>
       <c r="G71">
-        <v>-5.953239880405381</v>
+        <v>-6.602894953713419</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.2122222007711255</v>
       </c>
       <c r="E72">
-        <v>-3.703857307078939</v>
+        <v>-5.072618703768707</v>
       </c>
       <c r="F72">
-        <v>-0.07640130117510896</v>
+        <v>-1.046764130692895</v>
       </c>
       <c r="G72">
-        <v>-5.231763223395816</v>
+        <v>-6.460974877740502</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.5225216122209659</v>
       </c>
       <c r="E73">
-        <v>-2.53107764638518</v>
+        <v>-4.621218624507067</v>
       </c>
       <c r="F73">
-        <v>0.1270258521347824</v>
+        <v>-1.074406750924314</v>
       </c>
       <c r="G73">
-        <v>-6.276852115452237</v>
+        <v>-6.428972370542635</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.822832764505626</v>
       </c>
       <c r="E74">
-        <v>-3.917830754534106</v>
+        <v>-4.413466687616494</v>
       </c>
       <c r="F74">
-        <v>-0.2512091890856802</v>
+        <v>-1.123538878319158</v>
       </c>
       <c r="G74">
-        <v>-6.157473208278991</v>
+        <v>-6.315000315417584</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.106070197712453</v>
       </c>
       <c r="E75">
-        <v>-4.010484745979706</v>
+        <v>-4.79651736810543</v>
       </c>
       <c r="F75">
-        <v>-0.1883079387215026</v>
+        <v>-1.072681261624283</v>
       </c>
       <c r="G75">
-        <v>-5.310928831632143</v>
+        <v>-5.903844592741518</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.365962082196831</v>
       </c>
       <c r="E76">
-        <v>-5.630303614044034</v>
+        <v>-5.678210906675932</v>
       </c>
       <c r="F76">
-        <v>-0.760684963033877</v>
+        <v>-1.209520101260136</v>
       </c>
       <c r="G76">
-        <v>-5.252338501518379</v>
+        <v>-5.983070248103441</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.597291675496367</v>
       </c>
       <c r="E77">
-        <v>-3.606389743707863</v>
+        <v>-5.741630443606063</v>
       </c>
       <c r="F77">
-        <v>-0.2651746351294771</v>
+        <v>-0.8802183792578456</v>
       </c>
       <c r="G77">
-        <v>-4.562504068953107</v>
+        <v>-5.444186457051748</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.794687621931623</v>
       </c>
       <c r="E78">
-        <v>-5.471181628555878</v>
+        <v>-6.824895940615792</v>
       </c>
       <c r="F78">
-        <v>-0.5672280397840804</v>
+        <v>-1.335902459170451</v>
       </c>
       <c r="G78">
-        <v>-4.89788031912752</v>
+        <v>-5.183156380598468</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.953285569285115</v>
       </c>
       <c r="E79">
-        <v>-6.73944777081877</v>
+        <v>-6.338712716508714</v>
       </c>
       <c r="F79">
-        <v>-0.6327866927764388</v>
+        <v>-1.177947706069836</v>
       </c>
       <c r="G79">
-        <v>-4.951473684093893</v>
+        <v>-5.048804853195187</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.068647620755266</v>
       </c>
       <c r="E80">
-        <v>-6.093075185913055</v>
+        <v>-7.609902719544285</v>
       </c>
       <c r="F80">
-        <v>-0.1696845827717641</v>
+        <v>-1.084207994034238</v>
       </c>
       <c r="G80">
-        <v>-4.396646075824271</v>
+        <v>-4.734327613472637</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.138279948405057</v>
       </c>
       <c r="E81">
-        <v>-7.406308147189865</v>
+        <v>-8.204293711508447</v>
       </c>
       <c r="F81">
-        <v>-0.4822334024198371</v>
+        <v>-1.156622215652165</v>
       </c>
       <c r="G81">
-        <v>-3.956124697987362</v>
+        <v>-4.395539120117639</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.163026618501844</v>
       </c>
       <c r="E82">
-        <v>-7.664210110827742</v>
+        <v>-8.137107211906695</v>
       </c>
       <c r="F82">
-        <v>-0.4026488325632774</v>
+        <v>-1.39591022219665</v>
       </c>
       <c r="G82">
-        <v>-3.733206271075154</v>
+        <v>-4.123515198191181</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.146963286033925</v>
       </c>
       <c r="E83">
-        <v>-8.571516503638462</v>
+        <v>-9.063240111652862</v>
       </c>
       <c r="F83">
-        <v>-0.3576908485111399</v>
+        <v>-1.189906017896649</v>
       </c>
       <c r="G83">
-        <v>-4.116129401742922</v>
+        <v>-4.005982087443852</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.097818359440256</v>
       </c>
       <c r="E84">
-        <v>-8.823334012685466</v>
+        <v>-10.19513140685368</v>
       </c>
       <c r="F84">
-        <v>-0.5167025984177274</v>
+        <v>-1.569072972445261</v>
       </c>
       <c r="G84">
-        <v>-3.143538276237125</v>
+        <v>-3.767668099677849</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.030231378844656</v>
       </c>
       <c r="E85">
-        <v>-11.41526182986181</v>
+        <v>-11.20245543478892</v>
       </c>
       <c r="F85">
-        <v>-0.2334373948260196</v>
+        <v>-1.456392639744653</v>
       </c>
       <c r="G85">
-        <v>-3.110689887791737</v>
+        <v>-3.091333827393223</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.962412115702391</v>
       </c>
       <c r="E86">
-        <v>-11.11515493274103</v>
+        <v>-12.29623270966179</v>
       </c>
       <c r="F86">
-        <v>-0.6611880975488228</v>
+        <v>-1.041098097657746</v>
       </c>
       <c r="G86">
-        <v>-3.082687041307457</v>
+        <v>-2.958379048346188</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.914228833305246</v>
       </c>
       <c r="E87">
-        <v>-13.2721709196153</v>
+        <v>-13.76926462987271</v>
       </c>
       <c r="F87">
-        <v>-0.5134943314666849</v>
+        <v>-1.530822279253591</v>
       </c>
       <c r="G87">
-        <v>-2.900195994388638</v>
+        <v>-3.214824657297473</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.907974747609487</v>
       </c>
       <c r="E88">
-        <v>-15.34829896272722</v>
+        <v>-14.51493219113242</v>
       </c>
       <c r="F88">
-        <v>-0.5694654601390419</v>
+        <v>-1.803417282329839</v>
       </c>
       <c r="G88">
-        <v>-2.830750188265024</v>
+        <v>-3.132523544807218</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.961420329175054</v>
       </c>
       <c r="E89">
-        <v>-16.0789402054137</v>
+        <v>-17.17858596788856</v>
       </c>
       <c r="F89">
-        <v>-0.8081678109297474</v>
+        <v>-1.735675881231104</v>
       </c>
       <c r="G89">
-        <v>-2.451244522267024</v>
+        <v>-3.045449991204408</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.086294733946087</v>
       </c>
       <c r="E90">
-        <v>-19.40455772238896</v>
+        <v>-18.09928231401052</v>
       </c>
       <c r="F90">
-        <v>-0.4622854869930222</v>
+        <v>-1.507154994188207</v>
       </c>
       <c r="G90">
-        <v>-2.416156114962461</v>
+        <v>-2.346326529383954</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.289565694294264</v>
       </c>
       <c r="E91">
-        <v>-19.46849225752337</v>
+        <v>-19.49971610026343</v>
       </c>
       <c r="F91">
-        <v>-0.2833109110463695</v>
+        <v>-1.888522920926057</v>
       </c>
       <c r="G91">
-        <v>-2.472537755152143</v>
+        <v>-2.999174543326925</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.572564391256778</v>
       </c>
       <c r="E92">
-        <v>-22.15783364632357</v>
+        <v>-21.45922196937416</v>
       </c>
       <c r="F92">
-        <v>-0.3195453579796255</v>
+        <v>-1.976971021992571</v>
       </c>
       <c r="G92">
-        <v>-2.728082657219495</v>
+        <v>-2.771958830817744</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.926637602629934</v>
       </c>
       <c r="E93">
-        <v>-23.43745882155987</v>
+        <v>-22.94885427525042</v>
       </c>
       <c r="F93">
-        <v>-0.2593495555529909</v>
+        <v>-1.683760439362853</v>
       </c>
       <c r="G93">
-        <v>-2.509545059731174</v>
+        <v>-3.147788568431457</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.33358136859399</v>
       </c>
       <c r="E94">
-        <v>-25.64751131705221</v>
+        <v>-25.23602775183349</v>
       </c>
       <c r="F94">
-        <v>-0.03851840311028196</v>
+        <v>-1.788582878880505</v>
       </c>
       <c r="G94">
-        <v>-2.746240385850687</v>
+        <v>-2.803329537824562</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.774839374736684</v>
       </c>
       <c r="E95">
-        <v>-27.63479801671471</v>
+        <v>-28.01755381919959</v>
       </c>
       <c r="F95">
-        <v>-0.3530321102377955</v>
+        <v>-1.871962199809289</v>
       </c>
       <c r="G95">
-        <v>-2.746791252959412</v>
+        <v>-3.258058587726309</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.223918443620835</v>
       </c>
       <c r="E96">
-        <v>-30.22979505706011</v>
+        <v>-29.7540613126463</v>
       </c>
       <c r="F96">
-        <v>-0.7321750421317264</v>
+        <v>-1.865699742244125</v>
       </c>
       <c r="G96">
-        <v>-2.449578867217893</v>
+        <v>-3.615226723002744</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.651057541630503</v>
       </c>
       <c r="E97">
-        <v>-31.64355649845439</v>
+        <v>-32.77324659165306</v>
       </c>
       <c r="F97">
-        <v>-1.07074536700394</v>
+        <v>-1.90138663832413</v>
       </c>
       <c r="G97">
-        <v>-3.250440435009441</v>
+        <v>-4.10847992009096</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.032889885163407</v>
       </c>
       <c r="E98">
-        <v>-36.37169271376763</v>
+        <v>-34.34818793474695</v>
       </c>
       <c r="F98">
-        <v>-0.8679502580223849</v>
+        <v>-2.329948312734274</v>
       </c>
       <c r="G98">
-        <v>-3.091777653973713</v>
+        <v>-4.058664302547927</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.350035888893292</v>
       </c>
       <c r="E99">
-        <v>-39.168872234617</v>
+        <v>-37.00389869484435</v>
       </c>
       <c r="F99">
-        <v>-0.4752361829683897</v>
+        <v>-2.0972913872492</v>
       </c>
       <c r="G99">
-        <v>-3.827801379844961</v>
+        <v>-3.893944594060816</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.589404489992665</v>
       </c>
       <c r="E100">
-        <v>-40.39543182875597</v>
+        <v>-40.28113337649102</v>
       </c>
       <c r="F100">
-        <v>-0.854972225922725</v>
+        <v>-2.101645286318314</v>
       </c>
       <c r="G100">
-        <v>-3.122814185672868</v>
+        <v>-4.142683284979134</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.745713914472095</v>
       </c>
       <c r="E101">
-        <v>-42.81680594627257</v>
+        <v>-41.63122608827568</v>
       </c>
       <c r="F101">
-        <v>-1.02284833540667</v>
+        <v>-2.098456900184939</v>
       </c>
       <c r="G101">
-        <v>-4.020119269404731</v>
+        <v>-4.551345746570688</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.825504609552831</v>
       </c>
       <c r="E102">
-        <v>-45.1754582663616</v>
+        <v>-44.26188883087305</v>
       </c>
       <c r="F102">
-        <v>-1.039652596539861</v>
+        <v>-2.215413265418798</v>
       </c>
       <c r="G102">
-        <v>-3.694079041888139</v>
+        <v>-4.708609168505579</v>
       </c>
     </row>
   </sheetData>
